--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00984B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00984B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F101C19-8A9A-4EA7-B58D-A09B19C556B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{124A3DE2-1B13-462F-B1CD-6C3025E7337D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{63BB748E-CFF8-44AE-A9A9-AD917727AFC0}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{34BE8B18-9C8D-4EA9-B951-77541618B3AF}"/>
   </bookViews>
   <sheets>
     <sheet name="00984B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1465,24 +1465,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C10936C-5787-4E11-A0A3-5670A8D1254C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D74DC363-A731-4EC1-B65A-5C3A963FA0A6}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1511,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1541,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1586,7 +1587,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1636,7 +1637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2026</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="40"/>
@@ -1716,7 +1717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1828,7 +1829,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="45" t="s">
         <v>32</v>
       </c>
